--- a/data/processed/jfk_airline_delay_readable_full.xlsx
+++ b/data/processed/jfk_airline_delay_readable_full.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,102 +429,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>airline_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>airport_code</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>airport_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total_arrival_flights</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>delayed_arrivals_15_plus</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>estimated_delayed_arrivals_due_to_airline</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>estimated_delayed_arrivals_due_to_weather</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>estimated_delayed_arrivals_due_to_nas</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>estimated_delayed_arrivals_due_to_security</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>estimated_delayed_arrivals_due_to_late_aircraft</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>cancelled_arrivals</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>diverted_arrivals</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>total_arrival_delay_minutes</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>airline_delay_minutes</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>weather_delay_minutes</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>nas_delay_minutes</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>security_delay_minutes</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>late_aircraft_delay_minutes</t>
         </is>
@@ -2444,21 +2456,41 @@
           <t>John F. Kennedy International Airport (JFK)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -7433,7 +7465,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7977,7 +8009,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8589,7 +8621,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -9133,7 +9165,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9677,7 +9709,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10221,7 +10253,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -10765,7 +10797,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -11309,7 +11341,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -11853,7 +11885,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -12397,7 +12429,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -12941,7 +12973,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -13485,7 +13517,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -14029,7 +14061,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -14573,7 +14605,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -15117,7 +15149,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -15661,7 +15693,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -16205,7 +16237,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -16749,7 +16781,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -17293,7 +17325,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -17837,7 +17869,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United Air Lines Network</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
